--- a/public/exports-from-60/29189781.xlsx
+++ b/public/exports-from-60/29189781.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -12439,7 +12439,7 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311089558</t>
+          <t xml:space="preserve">311089559</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -12514,7 +12514,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311089558</t>
+          <t xml:space="preserve">311089559</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -12589,7 +12589,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311089558</t>
+          <t xml:space="preserve">311089559</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311089558</t>
+          <t xml:space="preserve">311089559</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">

--- a/public/exports-from-60/29189781.xlsx
+++ b/public/exports-from-60/29189781.xlsx
@@ -12739,7 +12739,7 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311089558</t>
+          <t xml:space="preserve">311089560</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -12889,7 +12889,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311089558</t>
+          <t xml:space="preserve">311089560</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -13039,7 +13039,7 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311089558</t>
+          <t xml:space="preserve">311089560</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -13264,7 +13264,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311089558</t>
+          <t xml:space="preserve">311089560</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -15754,12 +15754,12 @@
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -15829,12 +15829,12 @@
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>

--- a/public/exports-from-60/29189781.xlsx
+++ b/public/exports-from-60/29189781.xlsx
@@ -12439,7 +12439,7 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311089559</t>
+          <t xml:space="preserve">311089558</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -12514,7 +12514,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311089559</t>
+          <t xml:space="preserve">311089558</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -12589,7 +12589,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311089559</t>
+          <t xml:space="preserve">311089558</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -12739,7 +12739,7 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311089560</t>
+          <t xml:space="preserve">311089558</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311089559</t>
+          <t xml:space="preserve">311089558</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -12889,7 +12889,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311089560</t>
+          <t xml:space="preserve">311089558</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -13039,7 +13039,7 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311089560</t>
+          <t xml:space="preserve">311089558</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -13264,7 +13264,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311089560</t>
+          <t xml:space="preserve">311089558</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -15904,12 +15904,12 @@
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
